--- a/results/job_matches_2026-05-29.xlsx
+++ b/results/job_matches_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Application Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.5</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, Azure, GCP, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>AWS, Redshift, S3, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f2ea4b9227ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f021406866c8cb1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>25.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie</t>
+          <t>AWS, Redshift, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Oozie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f021406866c8cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=e788b64bde37944b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.7</v>
+        <v>24.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Oozie</t>
+          <t>AWS, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e788b64bde37944b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff822c60b8aee53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - AWS</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Great American Insurance Group</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
+          <t>AWS, Redshift, S3, ECS, RDS, Azure, Databricks, GCP, Cloud Storage, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84652629b44e36b8</t>
+          <t>https://www.indeed.com/viewjob?jk=28b17aa00b0fc706</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.3</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Scala, Kafka, Oracle</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, Data Lake Storage, GCP, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff822c60b8aee53</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5878406660b75c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Bread Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>24.3</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, ECS, RDS, Azure, Databricks, GCP, Cloud Storage, Hadoop</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Data Factory, Databricks, Blob Storage, Hadoop, HDFS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b17aa00b0fc706</t>
+          <t>https://www.indeed.com/viewjob?jk=beb7f5541ed44f4f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer- Application Development</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399227e084d1df1f</t>
+          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bread Financial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Data Factory, Databricks, Blob Storage, Hadoop, HDFS</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb7f5541ed44f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=db288f56e48736b6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Node JS Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db288f56e48736b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Node JS Developer</t>
+          <t>Azure Databrick Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
+          <t>https://www.indeed.com/viewjob?jk=11fb36e9daedb766</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>OSI Digital</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,54 +951,54 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab0c96b2af87c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OSI Digital</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
+          <t>https://www.indeed.com/viewjob?jk=8021a2f04b182e3d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Database Analyst</t>
+          <t>Senior Data Engineer (Snowflake)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Linqd</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,38 +1007,38 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Event Hubs, BigQuery, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f208d9b67253c76d</t>
+          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack Engineer (Contract)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8021a2f04b182e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>Philip Morris International</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5cdfdcc7f2368f7</t>
+          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alteryx Developer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Richmond</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,29 +1116,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cdfdcc7f2368f7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Alteryx Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Federal Reserve Bank of Richmond</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,59 +1151,59 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=512e38e26654ac89</t>
+          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Databricks, Spark, PySpark, Kafka, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f3dc197854ddef</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5d33bd00f9f4eb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,32 +1213,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70cde35cc4d9412</t>
+          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,32 +1248,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a84a3eeebaeb7c</t>
+          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,32 +1283,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4a43a12ff25318</t>
+          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,32 +1318,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f41679b052c9ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,32 +1353,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75f65db75d1108c6</t>
+          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,32 +1388,32 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f45269945ea9fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,32 +1423,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33835272b04dd982</t>
+          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,32 +1458,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df692083381730fc</t>
+          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b354f589377409f2</t>
+          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,32 +1528,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5d497ca1536ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,32 +1563,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6391ce83cfefb0</t>
+          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,32 +1598,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0284afbbb1c6e27c</t>
+          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,32 +1633,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff6b4227bbd6a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d477b7ef1fa32c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e08e91a3fb5f16</t>
+          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,32 +1738,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdfe43e2ebf0062</t>
+          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,32 +1773,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e8221df1c3723b</t>
+          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4afbb3652ab975</t>
+          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,32 +1843,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34d4a5c3530466d</t>
+          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,32 +1878,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f98ee94e2ffe2e</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,32 +1913,32 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de52551051f131f</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,32 +1948,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b60aecb70333e8</t>
+          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,32 +1983,32 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94db75d644163fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,32 +2018,32 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e0f9c0ea4636c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,32 +2053,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e856b53b948d15</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,32 +2088,32 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82d19bdd1498382</t>
+          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,32 +2123,32 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7edf21ea6b8feb</t>
+          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,32 +2158,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d54e37658f595d</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,32 +2193,32 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d0d09ac27ddb54</t>
+          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,32 +2228,32 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48942cdfb811e061</t>
+          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,32 +2263,32 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=635a8efd59211fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,32 +2298,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d022db1481834c5</t>
+          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,32 +2333,32 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11e3cd8c9574595a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,32 +2368,32 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf99ffa5bee240c6</t>
+          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,32 +2403,32 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664253218635fdb5</t>
+          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,32 +2438,32 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd722820ae31c360</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,470 +2473,470 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a801d42f61b42a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>DevOps Engineer (Terraform)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ef0c90d8f58ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=761cb5813df9068e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Sr. CRM Engineer | Cleveland, OH</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51dc0f54a87eacc8</t>
+          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=378564bcea2a3bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5333de330ea7934</t>
+          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614ad02f5e362d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b710809dd9d7a3</t>
+          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5128593a931439c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84c97f734a51d32</t>
+          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117ddd065e16bd17</t>
+          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad12ab4fee4e113</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4b800ec5bccaf</t>
+          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Developer/Senior Consultant</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ca37bcedb3ec5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Architect – Washington, DC</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9de31c9e29a5b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, Sqoop, Impala, Spark, PySpark, Scala, Kafka, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f4fcf4bdf627b93</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
+          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,102 +3051,102 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
+          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c9f21bfc2c673ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20df966ea532e3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
+          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Cleared Mid DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>HumanIT Solutions LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Beavercreek, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
+          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
+          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Cybersecurity Senior Engineer – Cloud Security</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=b2310c9c70a69a24</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>Cybersecurity Senior Engineer – Cloud Security</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ff16b9b763785e37</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
+          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
+          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Shaw Industries</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Dalton, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
+          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>DataBricks Data engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c253ac2f4a87b389</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Databrick Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Jasvik Solutions</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark, Scala, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf7dd433be6641f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Kdc Llc</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=93725c3dc0b45681</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a2e22fa42d1c49</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cleared Mid DevSecOps Engineer</t>
+          <t>Software Engineer - FICO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HumanIT Solutions LLC</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Beavercreek, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI-Accelerated Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a5277afe7a27c982</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cybersecurity Senior Engineer – Cloud Security</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
+          <t>AWS, Azure, Databricks, GCP, Hive, Spark, Scala, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2310c9c70a69a24</t>
+          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. AWS Cloud Engineer</t>
+          <t>Sr. Full Stack Developer – Java &amp; Spring Boot, Angular and AWS(Hybrid)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,50 +3733,50 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, IAM, RDS, Azure, Data Factory, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da439f0317feed08</t>
+          <t>https://www.indeed.com/viewjob?jk=649cdcb93d0df1cb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Architect – R01565908</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Holtzbrinck Publishing Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ac7aba73aa7703</t>
+          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
         </is>
       </c>
     </row>
@@ -3798,20 +3798,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DataBricks Data engineer</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c253ac2f4a87b389</t>
+          <t>https://www.indeed.com/viewjob?jk=0ae4fdc46bfe9f92</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>gWorks</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, IAM, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c782aadc2047f1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b9441dc19825f5b8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Programmer ETL Data Engineer</t>
+          <t>Apps Dev Analyst-Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c57ae65da4f36e79</t>
+          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer, Fleet Analytics, Cell Quality &amp; Field Reliability</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Convo LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Kafka, MySQL, MongoDB, ETL</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c653f5b18c837aab</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496e400decbd9200</t>
+          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2de466e9ede227</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,19 +4066,19 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804201ad9e2469c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4087,11 +4087,11 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b010f440df2e098</t>
+          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Architect - Iselin, NJ (Hybrid)</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Summit, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,67 +4136,67 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e17884e139d1340</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer - FICO</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
+          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Developer – Java &amp; Spring Boot, Angular and AWS(Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,102 +4206,102 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649cdcb93d0df1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=5c584f61b31ffef2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=24abd99c91cd3b59</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9e84045e2a59c7</t>
+          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Metronet</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ae4fdc46bfe9f92</t>
+          <t>https://www.indeed.com/viewjob?jk=aa494721f4ef838f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Azure Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>33Floors, LLC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9441dc19825f5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Apps Dev Analyst-Cloud Data Engineer</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
         </is>
       </c>
     </row>
@@ -4393,20 +4393,20 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BRUNT Workwear</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, ETL, ELT, dbt, Terraform, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,67 +4416,67 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae09a906dc9f4095</t>
+          <t>https://www.indeed.com/viewjob?jk=8de203e89eb9c66b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer – Platform Systems (Backend)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Terzo Enterprises</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016bba447faebcb6</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Full-Stack</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Convo LLC</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
+          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
+          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Software Engineer - .NET</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
+          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Business Intelligence Developer (Fabric)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>RedWeek.com</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
+          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer C1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c584f61b31ffef2</t>
+          <t>https://www.indeed.com/viewjob?jk=97271adf1cc8b05b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Senior Analytics &amp; Activation Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
         </is>
       </c>
     </row>
@@ -4778,20 +4778,20 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa494721f4ef838f</t>
+          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Azure Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>33Floors, LLC</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
+          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,102 +4871,102 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
+          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de203e89eb9c66b</t>
+          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ed94e1f1198b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer - Factory Automation</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>South Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b95a170038319d8</t>
+          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>RedWeek.com</t>
+          <t>RCN Capital, LLC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>South Windsor, CT, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
+          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack</t>
+          <t>Senior Software Engineer, Search Relevance</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
+          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Applications Engineer - General</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0733724faed40ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Applications Engineer - Engineering</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,67 +5116,67 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e79b06997ed521</t>
+          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Data Architect (LOC)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Scala, Kafka, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, RDS, Azure, Scala, Oracle</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a734af59193b4d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8355770dcb1b03</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Service Now Architect</t>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,602 +5186,42 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c738d13d9e81f79f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Sr Solutions Architect (Databricks)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>DBA</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edf9d5ab2f8e4574</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Software Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>TECHSTRA SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=229f3e749be7cca3</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>ritepros</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Portland, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>University of Maryland Medical System</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>North Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, HDFS, Hive, MapReduce, Spark, Scala, Oracle, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1315a3f918392bfc</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Analytics &amp; Activation Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>PlayStation</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Janus Henderson Investors</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>The Carlyle Group</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Blackfoot Telephone Cooperative</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Missoula, MT, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58ef3a1dce80d2c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>RCN Capital, LLC</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>South Windsor, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Search Relevance</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Box</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Data Architect (LOC)</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Ad Hoc</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, RDS, Azure, Scala, Oracle</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8355770dcb1b03</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Applications Engineer - General</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Varda Space Industries</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>El Segundo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Applications Engineer - Engineering</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Varda Space Industries</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>El Segundo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Systems Analyst</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Eastman Chemical</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Longview, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, SQL Server, ETL, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ab255a6d7bb4e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-29.xlsx
+++ b/results/job_matches_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
+          <t>Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=bad92e6915049edc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db288f56e48736b6</t>
+          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Node JS Developer</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ddd82b2a383f38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Databrick Engineer</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fb36e9daedb766</t>
+          <t>https://www.indeed.com/viewjob?jk=197d18130a300324</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Node JS Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Federal Home Loan Bank of Pittsburgh</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706e45c82f6dc417</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>(On-site) Biomedical Data Engineer - Rockefeller Neuroscience Institute</t>
+          <t>Azure Databrick Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>West Virginia University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Cloud Storage, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b89c5e1fd6c9b22</t>
+          <t>https://www.indeed.com/viewjob?jk=11fb36e9daedb766</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e338f14503b7dadc</t>
+          <t>https://www.indeed.com/viewjob?jk=bb221e9fbb9d1451</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Data Engineer, Mortgage Servicing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OSI Digital</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a17fe569b55d04</t>
+          <t>https://www.indeed.com/viewjob?jk=621d8acb024a7258</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Federal Home Loan Bank of Pittsburgh</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8021a2f04b182e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=706e45c82f6dc417</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake)</t>
+          <t>(On-site) Biomedical Data Engineer - Rockefeller Neuroscience Institute</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>West Virginia University</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
+          <t>https://www.indeed.com/viewjob?jk=2b89c5e1fd6c9b22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer (Contract)</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
+          <t>https://www.indeed.com/viewjob?jk=e338f14503b7dadc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Philip Morris International</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=8021a2f04b182e3d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Senior Data Engineer (Snowflake)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5cdfdcc7f2368f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alteryx Developer</t>
+          <t>Java Full Stack Engineer (Contract)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Richmond</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
+          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Philip Morris International</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Databricks, Spark, PySpark, Kafka, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5d33bd00f9f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
+          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cdfdcc7f2368f7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Alteryx Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Federal Reserve Bank of Richmond</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
+          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Databricks, Spark, PySpark, Kafka, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5d33bd00f9f4eb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
+          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
+          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
+          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
+          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
+          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
+          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
+          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
+          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
+          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
+          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
+          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
+          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
+          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
+          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
+          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
+          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
+          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
+          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
+          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
+          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Terraform)</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761cb5813df9068e</t>
+          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. CRM Engineer | Cleveland, OH</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
+          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
+          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>DevOps Engineer (Terraform)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
+          <t>https://www.indeed.com/viewjob?jk=761cb5813df9068e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Senior DevOps Programmer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Kafka, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1f2f6dd069879a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Sr. CRM Engineer | Cleveland, OH</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
+          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
+          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
+          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Senior Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
+          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
+          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
+          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
+          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cleared Mid DevSecOps Engineer</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HumanIT Solutions LLC</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Beavercreek, OH, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, IAM, RDS, Azure, GCP, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c1de8fbff52f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cybersecurity Senior Engineer – Cloud Security</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2310c9c70a69a24</t>
+          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cybersecurity Senior Engineer – Cloud Security</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff16b9b763785e37</t>
+          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
+          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, CI/CD</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,89 +3401,89 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
+          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Shaw Industries</t>
+          <t>Master Electronics</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dalton, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Hadoop, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
+          <t>https://www.indeed.com/viewjob?jk=d73436e1b1cecb10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
+          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DataBricks Data engineer</t>
+          <t>Cybersecurity Senior Engineer – Cloud Security</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3492,11 +3492,11 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c253ac2f4a87b389</t>
+          <t>https://www.indeed.com/viewjob?jk=b2310c9c70a69a24</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Azure Databrick Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jasvik Solutions</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark, Scala, Azure Cosmos DB</t>
+          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,172 +3541,172 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf7dd433be6641f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a4528c4b627821b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kdc Llc</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93725c3dc0b45681</t>
+          <t>https://www.indeed.com/viewjob?jk=2790efc31f46d191</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a2e22fa42d1c49</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer - FICO</t>
+          <t>Senior Backend Programmer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c33918a8076cae8</t>
+          <t>https://www.indeed.com/viewjob?jk=cd95e60f28e3747b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI-Accelerated Full Stack Software Development Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5277afe7a27c982</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Cybersecurity Senior Engineer – Cloud Security</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hive, Spark, Scala, ELT, MLOps, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
+          <t>https://www.indeed.com/viewjob?jk=ff16b9b763785e37</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Developer – Java &amp; Spring Boot, Angular and AWS(Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Sky Global Solutions</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649cdcb93d0df1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=216760c6e932824d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Holtzbrinck Publishing Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fec8a549c33ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ae4fdc46bfe9f92</t>
+          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Shaw Industries</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Dalton, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9441dc19825f5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Apps Dev Analyst-Cloud Data Engineer</t>
+          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DataBricks Data engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Convo LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
+          <t>https://www.indeed.com/viewjob?jk=c253ac2f4a87b389</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Azure Databrick Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Jasvik Solutions</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark, Scala, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,67 +3996,67 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf7dd433be6641f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Kdc Llc</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
+          <t>https://www.indeed.com/viewjob?jk=93725c3dc0b45681</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,67 +4066,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a2e22fa42d1c49</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3130fd4a42b451</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Hive, Spark, Scala, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
+          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Sr. Full Stack Developer – Java &amp; Spring Boot, Angular and AWS(Hybrid)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
+          <t>https://www.indeed.com/viewjob?jk=649cdcb93d0df1cb</t>
         </is>
       </c>
     </row>
@@ -4183,20 +4183,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c584f61b31ffef2</t>
+          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24abd99c91cd3b59</t>
+          <t>https://www.indeed.com/viewjob?jk=0ae4fdc46bfe9f92</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9441dc19825f5b8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Apps Dev Analyst-Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,137 +4311,137 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa494721f4ef838f</t>
+          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Azure Developer</t>
+          <t>Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>33Floors, LLC</t>
+          <t>SymphonyAI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
+          <t>https://www.indeed.com/viewjob?jk=7f23d596f24d9339</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Sr Data Engineer / Apache Cassandra Administrator</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>PDF Solutions, Inc</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Cassandra, NoSQL, Data Modeling, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5bb611379db114</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de203e89eb9c66b</t>
+          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Convo LLC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721fc28eba013089</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Fabric)</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
+          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RedWeek.com</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,67 +4661,67 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
+          <t>https://www.indeed.com/viewjob?jk=24abd99c91cd3b59</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DevOps Engineer C1</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97271adf1cc8b05b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Analytics &amp; Activation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Metronet</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
+          <t>https://www.indeed.com/viewjob?jk=aa494721f4ef838f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>33Floors, LLC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,49 +4836,49 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
+          <t>https://www.indeed.com/viewjob?jk=8de203e89eb9c66b</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4892,11 +4892,11 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Factory Automation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>RedWeek.com</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>South Portland, ME, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,102 +4976,102 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>RCN Capital, LLC</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>South Windsor, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Search Relevance</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Applications Engineer - General</t>
+          <t>Senior Software Engineer, Full-Stack</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,94 +5081,94 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4033ae48b4f5a15</t>
+          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Applications Engineer - Engineering</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=981c857c080d7a22</t>
+          <t>https://www.indeed.com/viewjob?jk=7a1ec1bcdc062275</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Architect (LOC)</t>
+          <t>Business Intelligence Developer (Fabric)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, RDS, Azure, Scala, Oracle</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8355770dcb1b03</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect (Databricks)</t>
+          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,17 +5211,717 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ritepros</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>DevOps Engineer C1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97271adf1cc8b05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Analytics &amp; Activation Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Janus Henderson Investors</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Security Specialist - Akamai Security Suite Administrator</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PNC Financial Services Group</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4e46c68109a11c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Shopify E-Commerce Architect Remote</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>David's Bridal</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=650a2db40b4383ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sr Solutions Architect (Databricks)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Zions Bancorporation</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Midvale, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HealthEdge</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior - MLOps/LLMOps Engineer, Development</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Citrin Cooperman Advisors LLC</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Sr Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Thousand Oaks, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Software Development Engineer - Factory Automation</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>South Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ecolab</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>RCN Capital, LLC</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>South Windsor, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Search Relevance</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Box</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Eastman Chemical</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Longview, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Data Factory, SQL Server, ETL, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2ab255a6d7bb4e9</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-29.xlsx
+++ b/results/job_matches_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,52 +643,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bread Financial</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Data Factory, Databricks, Blob Storage, Hadoop, HDFS</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb7f5541ed44f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6865e731762837d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bread Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Data Factory, Databricks, Blob Storage, Hadoop, HDFS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad92e6915049edc</t>
+          <t>https://www.indeed.com/viewjob?jk=beb7f5541ed44f4f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
+          <t>Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=bad92e6915049edc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ddd82b2a383f38</t>
+          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197d18130a300324</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ddd82b2a383f38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Node JS Developer</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
+          <t>https://www.indeed.com/viewjob?jk=197d18130a300324</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure Databrick Engineer</t>
+          <t>Node JS Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fb36e9daedb766</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb221e9fbb9d1451</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5dbf3e1be29598</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer, Mortgage Servicing</t>
+          <t>Azure Databrick Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621d8acb024a7258</t>
+          <t>https://www.indeed.com/viewjob?jk=11fb36e9daedb766</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alteryx Developer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Richmond</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
+          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Alteryx Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Federal Reserve Bank of Richmond</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Databricks, Spark, PySpark, Kafka, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5d33bd00f9f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Databricks, Spark, PySpark, Kafka, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5d33bd00f9f4eb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
+          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
+          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
+          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
+          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
+          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
+          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
+          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
+          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
+          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
+          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
+          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
+          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
+          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
+          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
+          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
+          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
+          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
+          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
+          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
+          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Terraform)</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761cb5813df9068e</t>
+          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Programmer</t>
+          <t>DevOps Engineer (Terraform)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Kafka, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1f2f6dd069879a</t>
+          <t>https://www.indeed.com/viewjob?jk=761cb5813df9068e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. CRM Engineer | Cleveland, OH</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
+          <t>https://www.indeed.com/viewjob?jk=7be7c12c113c7f4c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Programmer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Kafka, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1f2f6dd069879a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. CRM Engineer | Cleveland, OH</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
+          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
+          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
+          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Senior Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
+          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
+          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
+          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Master Electronics</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Hadoop, Spark, Scala, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73436e1b1cecb10</t>
+          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,312 +3471,312 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bbe1624133d599a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cybersecurity Senior Engineer – Cloud Security</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2310c9c70a69a24</t>
+          <t>https://www.indeed.com/viewjob?jk=b251bad156120ee9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Site AI Engineer - New Haven, CT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a4528c4b627821b</t>
+          <t>https://www.indeed.com/viewjob?jk=d29adf993445f0bd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Engineering Specialist</t>
+          <t>Site AI Engineer - Boston, MA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2790efc31f46d191</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Site AI Engineer - Temple, TX</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
+          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Backend Programmer</t>
+          <t>Site AI Engineer - Las Vegas, NV</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd95e60f28e3747b</t>
+          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Site AI Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Frontwave Credit Union</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
+          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cybersecurity Senior Engineer – Cloud Security</t>
+          <t>Site AI Engineer - Fort Meyers, FL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff16b9b763785e37</t>
+          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site AI Engineer - USVI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sky Global Solutions</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216760c6e932824d</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,102 +3786,102 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
+          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, CI/CD</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
+          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cybersecurity Senior Engineer – Cloud Security</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Shaw Industries</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dalton, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,164 +3891,164 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
+          <t>https://www.indeed.com/viewjob?jk=b2310c9c70a69a24</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DataBricks Data engineer</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c253ac2f4a87b389</t>
+          <t>https://www.indeed.com/viewjob?jk=2790efc31f46d191</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Azure Databrick Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jasvik Solutions</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark, Scala, Azure Cosmos DB</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf7dd433be6641f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Senior Backend Programmer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kdc Llc</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93725c3dc0b45681</t>
+          <t>https://www.indeed.com/viewjob?jk=cd95e60f28e3747b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Sky Global Solutions</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,102 +4066,102 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a2e22fa42d1c49</t>
+          <t>https://www.indeed.com/viewjob?jk=216760c6e932824d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3130fd4a42b451</t>
+          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Azure Full Stack Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Hiro Talent Solutions</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hive, Spark, Scala, ELT, MLOps, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
+          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Developer – Java &amp; Spring Boot, Angular and AWS(Hybrid)</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649cdcb93d0df1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
+          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Shaw Industries</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Dalton, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ae4fdc46bfe9f92</t>
+          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9441dc19825f5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Apps Dev Analyst-Cloud Data Engineer</t>
+          <t>DataBricks Data engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,54 +4311,54 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=c253ac2f4a87b389</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Solution Architect (Remote)</t>
+          <t>Azure Databrick Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SymphonyAI</t>
+          <t>Jasvik Solutions</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark, Scala, Azure Cosmos DB</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f23d596f24d9339</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf7dd433be6641f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr Data Engineer / Apache Cassandra Administrator</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PDF Solutions, Inc</t>
+          <t>Kdc Llc</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4367,81 +4367,81 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Cassandra, NoSQL, Data Modeling, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bb611379db114</t>
+          <t>https://www.indeed.com/viewjob?jk=93725c3dc0b45681</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>Sr Software Engineer (React, JavaScript, .net)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hagerstown, MD, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc464898e64c2d7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Convo LLC</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,67 +4451,67 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a2e22fa42d1c49</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3130fd4a42b451</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Hive, Spark, Scala, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
+          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Sr. Full Stack Developer – Java &amp; Spring Boot, Angular and AWS(Hybrid)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,19 +4556,19 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
+          <t>https://www.indeed.com/viewjob?jk=649cdcb93d0df1cb</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4577,11 +4577,11 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
+          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ae4fdc46bfe9f92</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,182 +4661,182 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
+          <t>https://www.indeed.com/viewjob?jk=b9441dc19825f5b8</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
+          <t>Apps Dev Analyst-Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24abd99c91cd3b59</t>
+          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=2099233b2412293a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa494721f4ef838f</t>
+          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Azure Developer</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>33Floors, LLC</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
+          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
         </is>
       </c>
     </row>
@@ -4848,47 +4848,47 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Convo LLC</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de203e89eb9c66b</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
+          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>RedWeek.com</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
+          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
+          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a1ec1bcdc062275</t>
+          <t>https://www.indeed.com/viewjob?jk=5c584f61b31ffef2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Fabric)</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,42 +5141,42 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
+          <t>https://www.indeed.com/viewjob?jk=24abd99c91cd3b59</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
+          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Metronet</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=aa494721f4ef838f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Developer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>33Floors, LLC</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,137 +5256,137 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DevOps Engineer C1</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ATI Physical Therapy</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97271adf1cc8b05b</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Analytics &amp; Activation Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
+          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,32 +5396,32 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,102 +5431,102 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
+          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Security Specialist - Akamai Security Suite Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e46c68109a11c2</t>
+          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Shopify E-Commerce Architect Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650a2db40b4383ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Software Engineer, Full-Stack</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,124 +5536,124 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect (Databricks)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>RedWeek.com</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
+          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer (Fabric)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>HealthEdge</t>
+          <t>ATI Physical Therapy</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
+          <t>https://www.indeed.com/viewjob?jk=e4139ecd61ccea47</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior - MLOps/LLMOps Engineer, Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Factory Automation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>South Portland, ME, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=dcdf9728d516c153</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>RCN Capital, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>South Windsor, CT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Search Relevance</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
+          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Systems Analyst</t>
+          <t>DevOps Engineer C1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Eastman Chemical</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Longview, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, SQL Server, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,7 +5921,707 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ab255a6d7bb4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=97271adf1cc8b05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior Analytics &amp; Activation Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Janus Henderson Investors</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Community</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>The New York Times</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2507171317a26faf</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, SharePoint</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Suffolk Construction</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Security Specialist - Akamai Security Suite Administrator</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PNC Financial Services Group</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4e46c68109a11c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Shopify E-Commerce Architect Remote</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>David's Bridal</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=650a2db40b4383ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sr Solutions Architect (Databricks)</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Zions Bancorporation</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Midvale, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>AI Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Suffolk Construction</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Digital Enterprise DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Arnold AFB, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Senior - MLOps/LLMOps Engineer, Development</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Citrin Cooperman Advisors LLC</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Sr Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Thousand Oaks, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Software Development Engineer - Factory Automation</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>South Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Ecolab</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>RCN Capital, LLC</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>South Windsor, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Search Relevance</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Box</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>HealthEdge</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-29.xlsx
+++ b/results/job_matches_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,52 +643,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bread Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Data Factory, Databricks, Blob Storage, Hadoop, HDFS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6865e731762837d</t>
+          <t>https://www.indeed.com/viewjob?jk=beb7f5541ed44f4f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bread Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Data Factory, Databricks, Blob Storage, Hadoop, HDFS</t>
+          <t>Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb7f5541ed44f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=bad92e6915049edc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad92e6915049edc</t>
+          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ddd82b2a383f38</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ddd82b2a383f38</t>
+          <t>https://www.indeed.com/viewjob?jk=197d18130a300324</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Node JS Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197d18130a300324</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Node JS Developer</t>
+          <t>Sr. Data Modeler</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
+          <t>https://www.indeed.com/viewjob?jk=633c48c04bec794a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Federal Home Loan Bank of Pittsburgh</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5dbf3e1be29598</t>
+          <t>https://www.indeed.com/viewjob?jk=706e45c82f6dc417</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure Databrick Engineer</t>
+          <t>(On-site) Biomedical Data Engineer - Rockefeller Neuroscience Institute</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>West Virginia University</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11fb36e9daedb766</t>
+          <t>https://www.indeed.com/viewjob?jk=2b89c5e1fd6c9b22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Federal Home Loan Bank of Pittsburgh</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706e45c82f6dc417</t>
+          <t>https://www.indeed.com/viewjob?jk=e338f14503b7dadc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>(On-site) Biomedical Data Engineer - Rockefeller Neuroscience Institute</t>
+          <t>Senior Data Engineer (Snowflake)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>West Virginia University</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Cloud Storage, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b89c5e1fd6c9b22</t>
+          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Java Full Stack Engineer (Contract)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e338f14503b7dadc</t>
+          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Philip Morris International</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8021a2f04b182e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer (Contract)</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,29 +1151,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cdfdcc7f2368f7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Philip Morris International</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Databricks, Spark, PySpark, Kafka, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5d33bd00f9f4eb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5cdfdcc7f2368f7</t>
+          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
+          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alteryx Developer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Richmond</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965d63ad9e6e8691</t>
+          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Databricks, Spark, PySpark, Kafka, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5d33bd00f9f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
+          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
+          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
+          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
+          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
+          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
+          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
+          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
+          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
+          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
+          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
+          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
+          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
+          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
+          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
+          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
+          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
+          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
+          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>DevOps Engineer (Terraform)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
+          <t>https://www.indeed.com/viewjob?jk=761cb5813df9068e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Data Architect - Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
+          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Senior DevOps Programmer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Kafka, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1f2f6dd069879a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Sr. CRM Engineer | Cleveland, OH</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
+          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Terraform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,129 +2701,129 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761cb5813df9068e</t>
+          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be7c12c113c7f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior DevOps Programmer</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Kafka, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1f2f6dd069879a</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. CRM Engineer | Cleveland, OH</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
+          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
+          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
+          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
+          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>IT Business Systems Analyst III - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
+          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
+          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
+          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
+          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
+          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=b251bad156120ee9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Site AI Engineer - New Haven, CT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=d29adf993445f0bd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site AI Engineer - Boston, MA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Site AI Engineer - Temple, TX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bbe1624133d599a</t>
+          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Site AI Engineer - Las Vegas, NV</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,24 +3496,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b251bad156120ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Site AI Engineer - New Haven, CT</t>
+          <t>Site AI Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3536,19 +3536,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29adf993445f0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Boston, MA</t>
+          <t>Site AI Engineer - Fort Meyers, FL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3571,19 +3571,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Temple, TX</t>
+          <t>Site AI Engineer - USVI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3606,169 +3606,169 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Las Vegas, NV</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
+          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Dallas, TX</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers, FL</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
+          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Site AI Engineer - USVI</t>
+          <t>Cybersecurity Senior Engineer – Cloud Security</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b2310c9c70a69a24</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2790efc31f46d191</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>Senior Backend Programmer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd95e60f28e3747b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cybersecurity Senior Engineer – Cloud Security</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,174 +3881,174 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2310c9c70a69a24</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Frontwave Credit Union</t>
+          <t>Sky Global Solutions</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
+          <t>https://www.indeed.com/viewjob?jk=216760c6e932824d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Engineering Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2790efc31f46d191</t>
+          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
+          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Backend Programmer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd95e60f28e3747b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sky Global Solutions</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216760c6e932824d</t>
+          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4318,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Azure Databrick Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jasvik Solutions</t>
+          <t>Kdc Llc</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark, Scala, Azure Cosmos DB</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf7dd433be6641f</t>
+          <t>https://www.indeed.com/viewjob?jk=93725c3dc0b45681</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kdc Llc</t>
+          <t>Key Prediction</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,17 +4371,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93725c3dc0b45681</t>
+          <t>https://www.indeed.com/viewjob?jk=b5586ae9539a9ac2</t>
         </is>
       </c>
     </row>
@@ -4703,17 +4703,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2099233b2412293a</t>
+          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Convo LLC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,42 +4826,42 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Convo LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
+          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
+          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
+          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
+          <t>https://www.indeed.com/viewjob?jk=5c584f61b31ffef2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c584f61b31ffef2</t>
+          <t>https://www.indeed.com/viewjob?jk=24abd99c91cd3b59</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24abd99c91cd3b59</t>
+          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Azure Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>33Floors, LLC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa494721f4ef838f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Azure Developer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>33Floors, LLC</t>
+          <t>ATI Physical Therapy</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
+          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ATI Physical Therapy</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
+          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer (Fabric)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,17 +5421,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
+          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Full-Stack</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
+          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>RedWeek.com</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>RedWeek.com</t>
+          <t>ATI Physical Therapy</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,42 +5561,42 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
+          <t>https://www.indeed.com/viewjob?jk=e4139ecd61ccea47</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Fabric)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,42 +5606,42 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
+          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ATI Physical Therapy</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4139ecd61ccea47</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
         </is>
       </c>
     </row>
@@ -5653,12 +5653,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
+          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
+          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>DevOps Engineer C1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcdf9728d516c153</t>
+          <t>https://www.indeed.com/viewjob?jk=97271adf1cc8b05b</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Analytics &amp; Activation Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
+          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
+          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DevOps Engineer C1</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97271adf1cc8b05b</t>
+          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Analytics &amp; Activation Engineer</t>
+          <t>Senior Software Engineer, Cloud Applications New</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, SharePoint</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
+          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Security Specialist - Akamai Security Suite Administrator</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e46c68109a11c2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Community</t>
+          <t>Shopify E-Commerce Architect Remote</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2507171317a26faf</t>
+          <t>https://www.indeed.com/viewjob?jk=650a2db40b4383ec</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, SharePoint</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Security Specialist - Akamai Security Suite Administrator</t>
+          <t>Sr Solutions Architect (Databricks)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e46c68109a11c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Shopify E-Commerce Architect Remote</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650a2db40b4383ec</t>
+          <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior - MLOps/LLMOps Engineer, Development</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
+          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect (Databricks)</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
+          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Software Development Engineer - Factory Automation</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>South Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
+          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Digital Enterprise DevSecOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Arnold AFB, TN, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
+          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior - MLOps/LLMOps Engineer, Development</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>RCN Capital, LLC</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>South Windsor, CT, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Software Engineer, Search Relevance</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
+          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Factory Automation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>South Portland, ME, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>HealthEdge</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Digital Enterprise DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>RCN Capital, LLC</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>South Windsor, CT, US USA</t>
+          <t>Arnold AFB, TN, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,157 +6471,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Search Relevance</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Box</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>BlackLine</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>HealthEdge</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>ServiceTitan</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e334cbfd67078a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-29.xlsx
+++ b/results/job_matches_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, Data Lake Storage, GCP, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f021406866c8cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5878406660b75c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Bread Financial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.7</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase, Oozie</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Data Factory, Databricks, Blob Storage, Hadoop, HDFS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e788b64bde37944b</t>
+          <t>https://www.indeed.com/viewjob?jk=beb7f5541ed44f4f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.3</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Hadoop, HDFS, Hive, Scala, Kafka, Oracle</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff822c60b8aee53</t>
+          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.3</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, ECS, RDS, Azure, Databricks, GCP, Cloud Storage, Hadoop</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b17aa00b0fc706</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ddd82b2a383f38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, Data Lake Storage, GCP, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5878406660b75c</t>
+          <t>https://www.indeed.com/viewjob?jk=197d18130a300324</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Modeler</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bread Financial</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Data Factory, Databricks, Blob Storage, Hadoop, HDFS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb7f5541ed44f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=633c48c04bec794a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad92e6915049edc</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>Federal Home Loan Bank of Pittsburgh</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=706e45c82f6dc417</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Software Engineer III - Big Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Sightview Software</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ddd82b2a383f38</t>
+          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Cloud Engineer - DevOps</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197d18130a300324</t>
+          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Node JS Developer</t>
+          <t>(On-site) Biomedical Data Engineer - Rockefeller Neuroscience Institute</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>West Virginia University</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b2f83e406090db</t>
+          <t>https://www.indeed.com/viewjob?jk=2b89c5e1fd6c9b22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c48c04bec794a</t>
+          <t>https://www.indeed.com/viewjob?jk=e338f14503b7dadc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer (Snowflake)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Federal Home Loan Bank of Pittsburgh</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706e45c82f6dc417</t>
+          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>(On-site) Biomedical Data Engineer - Rockefeller Neuroscience Institute</t>
+          <t>Java Full Stack Engineer (Contract)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>West Virginia University</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Cloud Storage, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b89c5e1fd6c9b22</t>
+          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Philip Morris International</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e338f14503b7dadc</t>
+          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer (Contract)</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
+          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Philip Morris International</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,112 +1081,112 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cdfdcc7f2368f7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Databricks, Spark, PySpark, Kafka, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5d33bd00f9f4eb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5cdfdcc7f2368f7</t>
+          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
+          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Databricks, Spark, PySpark, Kafka, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5d33bd00f9f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
+          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
+          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
+          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
+          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
+          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
+          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
+          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
+          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
+          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
+          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
+          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
+          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
+          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
+          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
+          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
+          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
+          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
+          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
+          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>DevOps Engineer (Terraform)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
+          <t>https://www.indeed.com/viewjob?jk=761cb5813df9068e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Data Architect - Remote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
+          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Senior DevOps Programmer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Kafka, MySQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1f2f6dd069879a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Terraform)</t>
+          <t>Sr. CRM Engineer | Cleveland, OH</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,129 +2561,129 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761cb5813df9068e</t>
+          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevOps Programmer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Kafka, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1f2f6dd069879a</t>
+          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. CRM Engineer | Cleveland, OH</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
+          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
+          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
+          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
+          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c90c2afa15db42</t>
+          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115b7bdca0e3472</t>
+          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,269 +2946,269 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf79e9d06453759</t>
+          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Data &amp; AI Intern</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b08aeedbd73fdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b9832efe0efb1942</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a29960bbdae701</t>
+          <t>https://www.indeed.com/viewjob?jk=b251bad156120ee9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst III - Remote</t>
+          <t>Site AI Engineer - New Haven, CT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ef0693d853058a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d29adf993445f0bd</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Site AI Engineer - Boston, MA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Site AI Engineer - Temple, TX</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
+          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Site AI Engineer - Las Vegas, NV</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
+          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Site AI Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Site AI Engineer - Fort Meyers, FL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site AI Engineer - USVI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,42 +3251,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,347 +3296,347 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0227bae85263e0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ELT</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c17d4cb02f0a19a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b251bad156120ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Site AI Engineer - New Haven, CT</t>
+          <t>Senior Application Security Engineer / AppSec Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29adf993445f0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8e7995889e5f42</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Boston, MA</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=2790efc31f46d191</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Temple, TX</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Las Vegas, NV</t>
+          <t>Senior Backend Programmer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
+          <t>https://www.indeed.com/viewjob?jk=cd95e60f28e3747b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Dallas, TX</t>
+          <t>Senior Database Administrator (Automation, Cloud &amp; Data Analytics)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=bfec1ad6856f8bb4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers, FL</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Site AI Engineer - USVI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Sky Global Solutions</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
+          <t>https://www.indeed.com/viewjob?jk=216760c6e932824d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
+          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,199 +3716,199 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cybersecurity Senior Engineer – Cloud Security</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2310c9c70a69a24</t>
+          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Engineering Specialist</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2790efc31f46d191</t>
+          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Azure Full Stack Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Hiro Talent Solutions</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
+          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Backend Programmer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd95e60f28e3747b</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Frontwave Credit Union</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
+          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sky Global Solutions</t>
+          <t>Shaw Industries</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dalton, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216760c6e932824d</t>
+          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>DataBricks Data engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c253ac2f4a87b389</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Kdc Llc</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
+          <t>https://www.indeed.com/viewjob?jk=93725c3dc0b45681</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Key Prediction</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
+          <t>https://www.indeed.com/viewjob?jk=b5586ae9539a9ac2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Forward Deployed Data Scientist Expert</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd2bca70b00b83</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Azure Full Stack Engineer</t>
+          <t>Forward Deployed Data Scientist Expert</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Hiro Talent Solutions</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
+          <t>https://www.indeed.com/viewjob?jk=5d5c7f6ae9c7f0ac</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Sr Software Engineer (React, JavaScript, .net)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Hagerstown, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc464898e64c2d7</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,207 +4206,207 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a2e22fa42d1c49</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Forward Deployed Data Engineer Expert</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Shaw Industries</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dalton, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
+          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DataBricks Data engineer</t>
+          <t>Forward Deployed Data Engineer Expert</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c253ac2f4a87b389</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3130fd4a42b451</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kdc Llc</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Hive, Spark, Scala, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93725c3dc0b45681</t>
+          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr. Full Stack Developer – Java &amp; Spring Boot, Angular and AWS(Hybrid)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Key Prediction</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5586ae9539a9ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=649cdcb93d0df1cb</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (React, JavaScript, .net)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hagerstown, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc464898e64c2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a2e22fa42d1c49</t>
+          <t>https://www.indeed.com/viewjob?jk=0ae4fdc46bfe9f92</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3130fd4a42b451</t>
+          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hive, Spark, Scala, ELT, MLOps, CI/CD</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Developer – Java &amp; Spring Boot, Angular and AWS(Hybrid)</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,77 +4546,77 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649cdcb93d0df1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>Mimecast</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ae4fdc46bfe9f92</t>
+          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9441dc19825f5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Apps Dev Analyst-Cloud Data Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,137 +4696,137 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aa4cf399071cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
+          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Convo LLC</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1ae9753a5ec281</t>
+          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Azure Developer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>33Floors, LLC</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Senior Data Engineer – Platform Foundation</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ATI Physical Therapy</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Auctane</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
+          <t>https://www.indeed.com/viewjob?jk=b98655cee0687224</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Associate MLOps Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
+          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>RedWeek.com</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c584f61b31ffef2</t>
+          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24abd99c91cd3b59</t>
+          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Azure Developer</t>
+          <t>Senior Software Engineer, Full-Stack</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>33Floors, LLC</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
+          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
+          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Business Intelligence Developer (Fabric)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ATI Physical Therapy</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>ATI Physical Therapy</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,77 +5281,77 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
+          <t>https://www.indeed.com/viewjob?jk=e4139ecd61ccea47</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
+          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
+          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Fabric)</t>
+          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,67 +5396,67 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
+          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,129 +5466,129 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
+          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
+          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>RedWeek.com</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
+          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ATI Physical Therapy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4139ecd61ccea47</t>
+          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics &amp; Activation Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
+          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Open Lending</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, Spark, Scala, ETL, ELT, Python</t>
+          <t>RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Maven, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc9efb7bf0927cb</t>
+          <t>https://www.indeed.com/viewjob?jk=02227c456a2f4e76</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Cloud Applications New</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Security Specialist - Akamai Security Suite Administrator</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e46c68109a11c2</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Shopify E-Commerce Architect Remote</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
+          <t>https://www.indeed.com/viewjob?jk=650a2db40b4383ec</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DevOps Engineer C1</t>
+          <t>Sr Solutions Architect (Databricks)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97271adf1cc8b05b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Analytics &amp; Activation Engineer</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
+          <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior - MLOps/LLMOps Engineer, Development</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
+          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528c2154e24d1767</t>
+          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Applications New</t>
+          <t>Senior Software Engineer, SharePoint</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
+          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, SharePoint</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Security Specialist - Akamai Security Suite Administrator</t>
+          <t>Software Development Engineer - Factory Automation</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>South Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e46c68109a11c2</t>
+          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Shopify E-Commerce Architect Remote</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650a2db40b4383ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>RCN Capital, LLC</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>South Windsor, CT, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
+          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect (Databricks)</t>
+          <t>Senior Software Engineer, Search Relevance</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
+          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,29 +6156,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
+          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior - MLOps/LLMOps Engineer, Development</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>HealthEdge</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
+          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Digital Enterprise DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Arnold AFB, TN, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,260 +6226,15 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Software Development Engineer - Factory Automation</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>South Portland, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Ecolab</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Eagan, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>RCN Capital, LLC</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>South Windsor, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Search Relevance</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Box</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>BlackLine</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>HealthEdge</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Digital Enterprise DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>BNH</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Arnold AFB, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
         </is>

--- a/results/job_matches_2026-05-29.xlsx
+++ b/results/job_matches_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Splunk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54cb6fb55273d2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Federal Home Loan Bank of Pittsburgh</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706e45c82f6dc417</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sightview Software</t>
+          <t>Federal Home Loan Bank of Pittsburgh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
+          <t>https://www.indeed.com/viewjob?jk=706e45c82f6dc417</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer - DevOps</t>
+          <t>Software Engineer III - Big Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>Sightview Software</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
+          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>(On-site) Biomedical Data Engineer - Rockefeller Neuroscience Institute</t>
+          <t>Cloud Engineer - DevOps</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>West Virginia University</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b89c5e1fd6c9b22</t>
+          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>(On-site) Biomedical Data Engineer - Rockefeller Neuroscience Institute</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>West Virginia University</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e338f14503b7dadc</t>
+          <t>https://www.indeed.com/viewjob?jk=2b89c5e1fd6c9b22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake)</t>
+          <t>Senior Data Engineer - IGEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer (Contract)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
+          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer (Snowflake)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Philip Morris International</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
+          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,112 +1081,112 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5cdfdcc7f2368f7</t>
+          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Databricks, Spark, PySpark, Kafka, Jenkins</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5d33bd00f9f4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Philip Morris International</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
+          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Java Full Stack Engineer (Contract)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Databricks, Spark, PySpark, Kafka, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5d33bd00f9f4eb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, IAM, RDS, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
+          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
+          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
+          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
+          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
+          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
+          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
+          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
+          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
+          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
+          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
+          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
+          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
+          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
+          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
+          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
+          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
+          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
+          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Terraform)</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761cb5813df9068e</t>
+          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect - Remote</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Programmer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Kafka, MySQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1f2f6dd069879a</t>
+          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. CRM Engineer | Cleveland, OH</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
+          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
+          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>DevOps Engineer (Terraform)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
+          <t>https://www.indeed.com/viewjob?jk=761cb5813df9068e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Data Architect - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>Sr. CRM Engineer | Cleveland, OH</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641ce19efe0be7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
+          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
+          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
+          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,77 +2866,77 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,129 +2946,129 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data &amp; AI Intern</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9832efe0efb1942</t>
+          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Centreville, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b251bad156120ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Site AI Engineer - New Haven, CT</t>
+          <t>Senior Data Architect / Data Engineer - 26-06256</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29adf993445f0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Boston, MA</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Temple, TX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
+          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Las Vegas, NV</t>
+          <t>Data &amp; AI Intern</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
+          <t>https://www.indeed.com/viewjob?jk=b9832efe0efb1942</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Dallas, TX</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,24 +3181,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=b251bad156120ee9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers, FL</t>
+          <t>Site AI Engineer - New Haven, CT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3221,19 +3221,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
+          <t>https://www.indeed.com/viewjob?jk=d29adf993445f0bd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Site AI Engineer - USVI</t>
+          <t>Site AI Engineer - Boston, MA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3256,204 +3256,204 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Site AI Engineer - Temple, TX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=582a5c2f09aaa3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>Site AI Engineer - Las Vegas, NV</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
+          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>Site AI Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer / AppSec Architect</t>
+          <t>Site AI Engineer - Fort Meyers, FL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8e7995889e5f42</t>
+          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Engineering Specialist</t>
+          <t>Site AI Engineer - USVI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2790efc31f46d191</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Backend Programmer</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd95e60f28e3747b</t>
+          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Database Administrator (Automation, Cloud &amp; Data Analytics)</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfec1ad6856f8bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Senior Application Security Engineer / AppSec Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Frontwave Credit Union</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,122 +3566,122 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8e7995889e5f42</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Administrator (Automation, Cloud &amp; Data Analytics)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sky Global Solutions</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216760c6e932824d</t>
+          <t>https://www.indeed.com/viewjob?jk=bfec1ad6856f8bb4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b48f611cc241ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
+          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
+          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
+          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Azure Full Stack Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hiro Talent Solutions</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
+          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Azure Full Stack Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Hiro Talent Solutions</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
+          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shaw Industries</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dalton, GA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
+          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Shaw Industries</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Dalton, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
+          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DataBricks Data engineer</t>
+          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c253ac2f4a87b389</t>
+          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
         </is>
       </c>
     </row>
@@ -4038,17 +4038,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI Engineer/Solution Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Key Prediction</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5586ae9539a9ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Scientist Expert</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd2bca70b00b83</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Scientist Expert</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d5c7f6ae9c7f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (React, JavaScript, .net)</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hagerstown, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc464898e64c2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,42 +4196,42 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a2e22fa42d1c49</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer Expert</t>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
+          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer Expert</t>
+          <t>Senior Sales Engineer, Commercial</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3130fd4a42b451</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6c3be2d26b87a0</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hive, Spark, Scala, ELT, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,59 +4346,59 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a2e22fa42d1c49</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Developer – Java &amp; Spring Boot, Angular and AWS(Hybrid)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Key Prediction</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649cdcb93d0df1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b5586ae9539a9ac2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Data Engineer Expert</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,24 +4406,24 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Irvington, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ae4fdc46bfe9f92</t>
+          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Forward Deployed Data Engineer Expert</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3130fd4a42b451</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Hive, Spark, Scala, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,217 +4546,217 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
+          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mimecast</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
+          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
+          <t>https://www.indeed.com/viewjob?jk=606aeb761182bb83</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
+          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
+          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Sr Software Engineer (React, JavaScript, .net)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hagerstown, MD, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc464898e64c2d7</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
+          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>Mimecast</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Azure Developer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>33Floors, LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee64cec38d7d125</t>
+          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Platform Foundation</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Snowflake, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0cede7ee8b6158</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ATI Physical Therapy</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Auctane</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b98655cee0687224</t>
+          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b5ea8333c0d680</t>
+          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Cost Engineer – Data Analytics</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>RedWeek.com</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3398e1df9137635</t>
+          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer / Database Management Specialist for Fish Data</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
+          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
+          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Full-Stack</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>ATI Physical Therapy</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MySQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd379d14e18e962c</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Auctane</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
+          <t>https://www.indeed.com/viewjob?jk=b98655cee0687224</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Fabric)</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
+          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ATI Physical Therapy</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,42 +5281,42 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4139ecd61ccea47</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior BI Analyst - IGEN</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SmartAsset</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
+          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
+          <t>Business Intelligence Developer (Fabric)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,67 +5396,67 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
+          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,59 +5466,59 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
+          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
+          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
+          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Analytics &amp; Activation Engineer</t>
+          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70aee5dcc1b2500</t>
+          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Open Lending</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Maven, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02227c456a2f4e76</t>
+          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Applications New</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
+          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Security Specialist - Akamai Security Suite Administrator</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e46c68109a11c2</t>
+          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Shopify E-Commerce Architect Remote</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Splunk, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650a2db40b4383ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect (Databricks)</t>
+          <t>Senior Analytics &amp; Activation Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
+          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Open Lending</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,29 +5841,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
+          <t>RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Maven, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
+          <t>https://www.indeed.com/viewjob?jk=02227c456a2f4e76</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior - MLOps/LLMOps Engineer, Development</t>
+          <t>Senior Software Engineer, Cloud Applications New</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Temporal Technologies</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
+          <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, SharePoint</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Analyst, Data Transfer Agreement, Gap Analysis, Data SQL Skills</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
+          <t>https://www.indeed.com/viewjob?jk=315a3a380566a99f</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Factory Automation</t>
+          <t>Senior - MLOps/LLMOps Engineer, Development</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>South Portland, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Solutions Architect (Databricks)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>RCN Capital, LLC</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>South Windsor, CT, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Search Relevance</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, ETL, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762e3894fad3e12a</t>
+          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, SharePoint</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>HealthEdge</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
+          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Digital Enterprise DevSecOps Engineer</t>
+          <t>Software Development Engineer - Factory Automation</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Arnold AFB, TN, US USA</t>
+          <t>South Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,15 +6226,190 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Ecolab</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>RCN Capital, LLC</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>South Windsor, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>HealthEdge</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Digital Enterprise DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Arnold AFB, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>2026-01-07</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
+      <c r="G171" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
         </is>

--- a/results/job_matches_2026-05-29.xlsx
+++ b/results/job_matches_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G171"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bread Financial</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Data Factory, Databricks, Blob Storage, Hadoop, HDFS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb7f5541ed44f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=096ec33d45508f2d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b88c69f0d47a40e9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ddd82b2a383f38</t>
+          <t>https://www.indeed.com/viewjob?jk=67aa72efa5b04e0c</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,94 +636,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197d18130a300324</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ddd82b2a383f38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c48c04bec794a</t>
+          <t>https://www.indeed.com/viewjob?jk=197d18130a300324</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr. Data Modeler</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d54cb6fb55273d2</t>
+          <t>https://www.indeed.com/viewjob?jk=633c48c04bec794a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
+          <t>https://www.indeed.com/viewjob?jk=7d54cb6fb55273d2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Federal Home Loan Bank of Pittsburgh</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706e45c82f6dc417</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>(On-site) Biomedical Data Engineer - Rockefeller Neuroscience Institute</t>
+          <t>Senior Data Engineer - IGEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>West Virginia University</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Cloud Storage, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b89c5e1fd6c9b22</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - IGEN</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
+          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Engineer (Snowflake)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>VSP Vision</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
+          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake)</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06419a6d15ac391</t>
+          <t>https://www.indeed.com/viewjob?jk=47fb9412169ca299</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Philip Morris International</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
+          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
+          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
+          <t>https://www.indeed.com/viewjob?jk=1cd40cf715d1757e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
+          <t>https://www.indeed.com/viewjob?jk=c3efe7a4e50700ee</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Philip Morris International</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=3185efffc8151880</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
+          <t>https://www.indeed.com/viewjob?jk=b53f7ddb0026dea4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer (Contract)</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AXIAN</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf3b9815a50b381</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Java Full Stack Engineer (Contract)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AXIAN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
+          <t>https://www.indeed.com/viewjob?jk=91333a1bd534aa31</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect - Remote</t>
+          <t>Senior Data Solutions Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. CRM Engineer | Cleveland, OH</t>
+          <t>Data Architect - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,69 +2726,69 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
+          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. CRM Engineer | Cleveland, OH</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=58b880cbe2164f42</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Kafka, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
+          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, Informatica PowerCenter, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd2d99f50f24a3c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
+          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,174 +2901,174 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e4adfa75de057b</t>
+          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
+          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
+          <t>https://www.indeed.com/viewjob?jk=1aa9a1ae247379c0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Data &amp; AI Intern</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
+          <t>https://www.indeed.com/viewjob?jk=b9832efe0efb1942</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Aptean</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef802648dc8c758d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Site AI Engineer - New Haven, CT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=d29adf993445f0bd</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site AI Engineer - Boston, MA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data &amp; AI Intern</t>
+          <t>Site AI Engineer - Temple, TX</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9832efe0efb1942</t>
+          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Site AI Engineer - Las Vegas, NV</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,24 +3181,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b251bad156120ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Site AI Engineer - New Haven, CT</t>
+          <t>Site AI Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3221,19 +3221,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29adf993445f0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Boston, MA</t>
+          <t>Site AI Engineer - Fort Meyers, FL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3256,19 +3256,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Temple, TX</t>
+          <t>Site AI Engineer - USVI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3291,169 +3291,169 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Las Vegas, NV</t>
+          <t>Sr. DevOps Engineer- Snowflake &amp; Azure</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
+          <t>https://www.indeed.com/viewjob?jk=763fd8f53ea47c3f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Dallas, TX</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers, FL</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
+          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Site AI Engineer - USVI</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
+          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Solutions Architect - Emerging</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7afdce6cf8faaddf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ce1a2957006a72</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer (Agent Systems)</t>
+          <t>Senior Application Security Engineer / AppSec Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Faraday Future</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>S3, RDS, BigQuery, Spark, Kafka, Snowflake, PostgreSQL, MySQL, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8e7995889e5f42</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer / AppSec Architect</t>
+          <t>Senior Database Administrator (Automation, Cloud &amp; Data Analytics)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8e7995889e5f42</t>
+          <t>https://www.indeed.com/viewjob?jk=bfec1ad6856f8bb4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Database Administrator (Automation, Cloud &amp; Data Analytics)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfec1ad6856f8bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,52 +3636,52 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Frontwave Credit Union</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
+          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
+          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
+          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Azure Full Stack Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Hiro Talent Solutions</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
+          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Azure Full Stack Engineer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hiro Talent Solutions</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
+          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
+          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Shaw Industries</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Dalton, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, CI/CD</t>
+          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
+          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Shaw Industries</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dalton, GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
+          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Kdc Llc</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
+          <t>https://www.indeed.com/viewjob?jk=93725c3dc0b45681</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kdc Llc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93725c3dc0b45681</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0bc73a9e9547ac</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Engineer/Solution Architect</t>
+          <t>Software Engineer II - Full Stack Java</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
+          <t>https://www.indeed.com/viewjob?jk=2c274b0f05e69603</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Product Foundations</t>
+          <t>AI Engineer/Solution Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, SQS, IAM, RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Full Stack Developer -In office, Alpharetta, GA</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
+          <t>Full Stack Developer -In office, Alpharetta, GA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=adcfd5cf564b5b00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer 4</t>
+          <t>Cloud Data Architect (Full-time Remote, NC Based)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Castlight</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb114578f5bf1e9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6c3be2d26b87a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4533,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
+          <t>https://www.indeed.com/viewjob?jk=e257db597eccae8d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer, II</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
+          <t>https://www.indeed.com/viewjob?jk=22172251f6a1ea83</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606aeb761182bb83</t>
+          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Sr. Solutions Engineer - GSI's and FinTech Data</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=44ec35e1f7566eb4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Solutions Architect - Emerging Enterprise (Startups)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f72901b7b29fed1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Engineering Specialist</t>
+          <t>Sr. Solutions Engineer - Financial Services (Insurance)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
+          <t>https://www.indeed.com/viewjob?jk=df17d8e1960c7150</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (React, JavaScript, .net)</t>
+          <t>Solutions Architect - Emerging Enterprise</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hagerstown, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,42 +4756,42 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc464898e64c2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=05e7797d12dd5834</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr. Solutions Architect - Financial Services (Wealth and Asset Management)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
+          <t>https://www.indeed.com/viewjob?jk=b25a6a580453b9d6</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mimecast</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,172 +4836,172 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a9b5d614307098</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Solutions Architect - MFG</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e100201c444a83c</t>
+          <t>https://www.indeed.com/viewjob?jk=4aad818a2ea4d82e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0e7d846c8a2243</t>
+          <t>https://www.indeed.com/viewjob?jk=606aeb761182bb83</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbbfbfd6ef656e4</t>
+          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca22b19d31d8387</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Sr Software Engineer (React, JavaScript, .net)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hagerstown, MD, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, Data Modeling, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,59 +5011,59 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd2508274e7a97e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc464898e64c2d7</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SoftSoftware Engineer 2 Software Engineer 2 (API /NodeJS /Javascript)</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ETL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744e9b68aa73ba93</t>
+          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Cost Engineer – Data Analytics</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a2644095339b05a5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer / Database Management Specialist for Fish Data</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
+          <t>Mimecast</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, SQS, RDS, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Cost Engineer – Data Analytics</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Engineer / Database Management Specialist for Fish Data</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ATI Physical Therapy</t>
+          <t>PACIFIC STATES MARINE FISHERIES COMMISSION</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
+          <t>https://www.indeed.com/viewjob?jk=47ce35760bca7d80</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Auctane</t>
+          <t>ATI Physical Therapy</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b98655cee0687224</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9e3e8db4c59f0</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Resident Solutions Architect - Digital Native Business</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
+          <t>https://www.indeed.com/viewjob?jk=604425795ad5683a</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff1bc3eed7d9ae60</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior BI Analyst - IGEN</t>
+          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b19a38637eb42</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
+          <t>https://www.indeed.com/viewjob?jk=c37498a6699ecacb</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Fabric)</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
+          <t>https://www.indeed.com/viewjob?jk=ca97d35c293c8ce6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Auctane</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
+          <t>https://www.indeed.com/viewjob?jk=b98655cee0687224</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
+          <t>https://www.indeed.com/viewjob?jk=8fda6cb70fb70e09</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,42 +5491,42 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd22b9c4b47341c</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior BI Analyst - IGEN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SmartAsset</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, dbt, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
+          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>Redshift, RDS, Databricks, Scala, Oracle, MySQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,32 +5571,32 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
+          <t>https://www.indeed.com/viewjob?jk=95ab2514764a8e05</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
+          <t>Business Intelligence Developer (Fabric)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,67 +5606,67 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e60194d70d8d72</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
+          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,59 +5676,59 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
+          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, ECS, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
+          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
+          <t>https://www.indeed.com/viewjob?jk=d95d0b3cc2017278</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Analytics &amp; Activation Engineer</t>
+          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, dbt, CI/CD, Python</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e4e54b6bcc6235</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Open Lending</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Maven, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02227c456a2f4e76</t>
+          <t>https://www.indeed.com/viewjob?jk=392c5b4963d57266</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Applications New</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Spokane Valley, WA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
+          <t>https://www.indeed.com/viewjob?jk=05b11f37b58c06df</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e166dda8b8fb2c2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Gesa Credit Union</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Richland, WA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, NoSQL, Data Modeling, Python</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
+          <t>https://www.indeed.com/viewjob?jk=38d66edddd66e10c</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Data Analyst, Data Transfer Agreement, Gap Analysis, Data SQL Skills</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=315a3a380566a99f</t>
+          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior - MLOps/LLMOps Engineer, Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
+          <t>https://www.indeed.com/viewjob?jk=db40921aad59c33b</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
+          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect (Databricks)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,29 +6086,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
+          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
+          <t>https://www.indeed.com/viewjob?jk=85ead362a062186e</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, SharePoint</t>
+          <t>Resident Solutions Architect - Manufacturing</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6a09c3cec51934e4</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
+          <t>https://www.indeed.com/viewjob?jk=38625ef404e5c4f3</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Factory Automation</t>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>South Portland, ME, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e1163fe26a7f0c</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=300acc8c1eb7c502</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>RCN Capital, LLC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>South Windsor, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f223dfd349f07c12</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resident Solutions Architect - Financial Services</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
+          <t>https://www.indeed.com/viewjob?jk=91a31dc96a52eccd</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HealthEdge</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
+          <t>https://www.indeed.com/viewjob?jk=7db4000add37c391</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Digital Enterprise DevSecOps Engineer</t>
+          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Arnold AFB, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,15 +6401,1520 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7770787ca90c8b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Manufacturing</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bab1eb82e51a467</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Financial Services</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=427fc18bf3e71e29</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Manufacturing</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a54c94417b741d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Financial Services</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9586c99c5eb6653</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37f9f241665f8f25</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdd06f296c307d2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4297244e8d171dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Financial Services</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6fbdbfa7f478c1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0759cd4fbd6bdac8</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Financial Services</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94317beda0e6b715</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b8ceabdc300636a</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=822d767e26112ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81b64f7562795fab</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d113953416ca6dbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Manufacturing</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fc84e05f0d0c4f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Financial Services</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1ed17e2895f23aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9519050e585036f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22686cead31117d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Sr. Resident Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Central, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75153db402f3d420</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e46c18319f67321a</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Resident Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=687bf527e281aa97</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Database Architect</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64c482ee7d2fd8be</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Digital Native Business, Strategic</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42e61be032685e36</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Architect - Strategic AI Native</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e74525fcfa96e5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer - AI Natives Business</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d884fcaeec353d16</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Architect - AI Natives Business</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29b6a8557301e33c</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Software Architect</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>PNC Financial Services Group</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Oracle, MongoDB, Splunk, Jenkins, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80790f8d8ef27b8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Open Lending</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Maven, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02227c456a2f4e76</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Cloud Applications New</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Temporal Technologies</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Kinesis, Redshift, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Alight Solutions</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b971d4cbb76a50f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Senior - MLOps/LLMOps Engineer, Development</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Citrin Cooperman Advisors LLC</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Sr Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Thousand Oaks, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, ETL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Sr Solutions Architect (Databricks)</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Zions Bancorporation</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Midvale, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Google Cloud Platform, GCP, Spark, ETL</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e6b21cb550cfb29</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>AI Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Suffolk Construction</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Zoom Communications</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6b981d8b3e30244</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Teza Technologies</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8521b827213a9dde</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, SharePoint</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Suffolk Construction</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Scala, SQL Server, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8916dfa1faff9d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df1553e436d1437f</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Software Development Engineer - Factory Automation</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>South Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Ecolab</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7120ef72a814fea5</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>HealthEdge</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Digital Enterprise DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Arnold AFB, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>2026-01-07</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
         </is>
